--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427386</v>
+        <v>122427282</v>
       </c>
       <c r="B3" t="n">
-        <v>90809</v>
+        <v>78291</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561658</v>
+        <v>561708</v>
       </c>
       <c r="R3" t="n">
-        <v>6516859</v>
+        <v>6516850</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427988</v>
+        <v>122427208</v>
       </c>
       <c r="B4" t="n">
-        <v>78646</v>
+        <v>94850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561776</v>
+        <v>561708</v>
       </c>
       <c r="R4" t="n">
-        <v>6517066</v>
+        <v>6516850</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427347</v>
+        <v>122427988</v>
       </c>
       <c r="B5" t="n">
-        <v>94850</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561686</v>
+        <v>561776</v>
       </c>
       <c r="R5" t="n">
-        <v>6516859</v>
+        <v>6517066</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427282</v>
+        <v>122429431</v>
       </c>
       <c r="B6" t="n">
-        <v>78291</v>
+        <v>105290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561708</v>
+        <v>561619</v>
       </c>
       <c r="R6" t="n">
-        <v>6516850</v>
+        <v>6516592</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427208</v>
+        <v>122427347</v>
       </c>
       <c r="B7" t="n">
         <v>94850</v>
@@ -1221,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561708</v>
+        <v>561686</v>
       </c>
       <c r="R7" t="n">
-        <v>6516850</v>
+        <v>6516859</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429431</v>
+        <v>122427386</v>
       </c>
       <c r="B8" t="n">
-        <v>105290</v>
+        <v>90809</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561619</v>
+        <v>561658</v>
       </c>
       <c r="R8" t="n">
-        <v>6516592</v>
+        <v>6516859</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429431</v>
+        <v>122427347</v>
       </c>
       <c r="B6" t="n">
-        <v>105290</v>
+        <v>94850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561619</v>
+        <v>561686</v>
       </c>
       <c r="R6" t="n">
-        <v>6516592</v>
+        <v>6516859</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427347</v>
+        <v>122429431</v>
       </c>
       <c r="B7" t="n">
-        <v>94850</v>
+        <v>105290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561686</v>
+        <v>561619</v>
       </c>
       <c r="R7" t="n">
-        <v>6516859</v>
+        <v>6516592</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122426577</v>
+        <v>122427988</v>
       </c>
       <c r="B2" t="n">
-        <v>94850</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561634</v>
+        <v>561776</v>
       </c>
       <c r="R2" t="n">
-        <v>6516928</v>
+        <v>6517066</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427282</v>
+        <v>122427208</v>
       </c>
       <c r="B3" t="n">
-        <v>78291</v>
+        <v>94862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427208</v>
+        <v>122426577</v>
       </c>
       <c r="B4" t="n">
-        <v>94850</v>
+        <v>94862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R4" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427988</v>
+        <v>122427282</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>78296</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561776</v>
+        <v>561708</v>
       </c>
       <c r="R5" t="n">
-        <v>6517066</v>
+        <v>6516850</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>122427347</v>
       </c>
       <c r="B6" t="n">
-        <v>94850</v>
+        <v>94862</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>122429431</v>
       </c>
       <c r="B7" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>122427386</v>
       </c>
       <c r="B8" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,6 +1386,220 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122477989</v>
+      </c>
+      <c r="B9" t="n">
+        <v>94974</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Orrmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>561816</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6517001</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122478011</v>
+      </c>
+      <c r="B10" t="n">
+        <v>94867</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Orrmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>561593</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6516888</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skedevi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122427988</v>
+        <v>122427347</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>94867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561776</v>
+        <v>561686</v>
       </c>
       <c r="R2" t="n">
-        <v>6517066</v>
+        <v>6516859</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427208</v>
+        <v>122427282</v>
       </c>
       <c r="B3" t="n">
-        <v>94862</v>
+        <v>78296</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122426577</v>
+        <v>122429431</v>
       </c>
       <c r="B4" t="n">
-        <v>94862</v>
+        <v>105308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561634</v>
+        <v>561619</v>
       </c>
       <c r="R4" t="n">
-        <v>6516928</v>
+        <v>6516592</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427282</v>
+        <v>122427208</v>
       </c>
       <c r="B5" t="n">
-        <v>78296</v>
+        <v>94867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427347</v>
+        <v>122427988</v>
       </c>
       <c r="B6" t="n">
-        <v>94862</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561686</v>
+        <v>561776</v>
       </c>
       <c r="R6" t="n">
-        <v>6516859</v>
+        <v>6517066</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122429431</v>
+        <v>122426577</v>
       </c>
       <c r="B7" t="n">
-        <v>105303</v>
+        <v>94867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561619</v>
+        <v>561634</v>
       </c>
       <c r="R7" t="n">
-        <v>6516592</v>
+        <v>6516928</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
         <v>122427386</v>
       </c>
       <c r="B8" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122427347</v>
       </c>
       <c r="B2" t="n">
-        <v>94867</v>
+        <v>94876</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>2170</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427282</v>
+        <v>122426577</v>
       </c>
       <c r="B3" t="n">
-        <v>78296</v>
+        <v>94876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +784,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
+        <v>2170</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R3" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429431</v>
+        <v>122427282</v>
       </c>
       <c r="B4" t="n">
-        <v>105308</v>
+        <v>78297</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +881,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>353</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561619</v>
+        <v>561708</v>
       </c>
       <c r="R4" t="n">
-        <v>6516592</v>
+        <v>6516850</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427208</v>
+        <v>122427386</v>
       </c>
       <c r="B5" t="n">
-        <v>94867</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +978,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561708</v>
+        <v>561658</v>
       </c>
       <c r="R5" t="n">
-        <v>6516850</v>
+        <v>6516859</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427988</v>
+        <v>122427208</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>94876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1075,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>2170</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561776</v>
+        <v>561708</v>
       </c>
       <c r="R6" t="n">
-        <v>6517066</v>
+        <v>6516850</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122426577</v>
+        <v>122427988</v>
       </c>
       <c r="B7" t="n">
-        <v>94867</v>
+        <v>78652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1172,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561634</v>
+        <v>561776</v>
       </c>
       <c r="R7" t="n">
-        <v>6516928</v>
+        <v>6517066</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427386</v>
+        <v>122429431</v>
       </c>
       <c r="B8" t="n">
-        <v>90828</v>
+        <v>105317</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1269,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561658</v>
+        <v>561619</v>
       </c>
       <c r="R8" t="n">
-        <v>6516859</v>
+        <v>6516592</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1357,7 @@
         <v>122477989</v>
       </c>
       <c r="B9" t="n">
-        <v>94974</v>
+        <v>94983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,11 +1371,6 @@
       </c>
       <c r="E9" t="n">
         <v>2180</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1499,7 +1459,7 @@
         <v>122478011</v>
       </c>
       <c r="B10" t="n">
-        <v>94867</v>
+        <v>94876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,11 +1473,6 @@
       </c>
       <c r="E10" t="n">
         <v>2170</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122426577</v>
+        <v>122427282</v>
       </c>
       <c r="B3" t="n">
-        <v>94876</v>
+        <v>78297</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -784,36 +784,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561634</v>
+        <v>561708</v>
       </c>
       <c r="R3" t="n">
-        <v>6516928</v>
+        <v>6516850</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427282</v>
+        <v>122426577</v>
       </c>
       <c r="B4" t="n">
-        <v>78297</v>
+        <v>94876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -881,36 +881,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R4" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122427347</v>
+        <v>122427282</v>
       </c>
       <c r="B2" t="n">
-        <v>94876</v>
+        <v>78301</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>353</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561686</v>
+        <v>561708</v>
       </c>
       <c r="R2" t="n">
-        <v>6516859</v>
+        <v>6516850</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427282</v>
+        <v>122427386</v>
       </c>
       <c r="B3" t="n">
-        <v>78297</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,16 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561708</v>
+        <v>561658</v>
       </c>
       <c r="R3" t="n">
-        <v>6516850</v>
+        <v>6516859</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122426577</v>
+        <v>122429431</v>
       </c>
       <c r="B4" t="n">
-        <v>94876</v>
+        <v>105330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -885,32 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561634</v>
+        <v>561619</v>
       </c>
       <c r="R4" t="n">
-        <v>6516928</v>
+        <v>6516592</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427386</v>
+        <v>122427347</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>94889</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -978,36 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>2170</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561658</v>
+        <v>561686</v>
       </c>
       <c r="R5" t="n">
         <v>6516859</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427208</v>
+        <v>122426577</v>
       </c>
       <c r="B6" t="n">
-        <v>94876</v>
+        <v>94889</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1081,6 +1101,11 @@
       <c r="E6" t="n">
         <v>2170</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Dicranum flagellare</t>
@@ -1094,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R6" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1188,7 @@
         <v>122427988</v>
       </c>
       <c r="B7" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1177,6 +1202,11 @@
       </c>
       <c r="E7" t="n">
         <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1257,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429431</v>
+        <v>122427208</v>
       </c>
       <c r="B8" t="n">
-        <v>105317</v>
+        <v>94889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1273,32 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>2170</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561619</v>
+        <v>561708</v>
       </c>
       <c r="R8" t="n">
-        <v>6516592</v>
+        <v>6516850</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1354,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122477989</v>
+        <v>122478011</v>
       </c>
       <c r="B9" t="n">
-        <v>94983</v>
+        <v>94889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1370,16 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>2170</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1393,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561816</v>
+        <v>561593</v>
       </c>
       <c r="R9" t="n">
-        <v>6517001</v>
+        <v>6516888</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1456,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478011</v>
+        <v>122477989</v>
       </c>
       <c r="B10" t="n">
-        <v>94876</v>
+        <v>94996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1472,16 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>2180</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561593</v>
+        <v>561816</v>
       </c>
       <c r="R10" t="n">
-        <v>6516888</v>
+        <v>6517001</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427386</v>
+        <v>122427347</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>94902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561658</v>
+        <v>561686</v>
       </c>
       <c r="R3" t="n">
         <v>6516859</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>122429431</v>
       </c>
       <c r="B4" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427347</v>
+        <v>122427208</v>
       </c>
       <c r="B5" t="n">
-        <v>94889</v>
+        <v>94902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561686</v>
+        <v>561708</v>
       </c>
       <c r="R5" t="n">
-        <v>6516859</v>
+        <v>6516850</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122426577</v>
+        <v>122427386</v>
       </c>
       <c r="B6" t="n">
-        <v>94889</v>
+        <v>90859</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561634</v>
+        <v>561658</v>
       </c>
       <c r="R6" t="n">
-        <v>6516928</v>
+        <v>6516859</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427988</v>
+        <v>122426577</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>94902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561776</v>
+        <v>561634</v>
       </c>
       <c r="R7" t="n">
-        <v>6517066</v>
+        <v>6516928</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427208</v>
+        <v>122427988</v>
       </c>
       <c r="B8" t="n">
-        <v>94889</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561708</v>
+        <v>561776</v>
       </c>
       <c r="R8" t="n">
-        <v>6516850</v>
+        <v>6517066</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478011</v>
+        <v>122477989</v>
       </c>
       <c r="B9" t="n">
-        <v>94889</v>
+        <v>95009</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561593</v>
+        <v>561816</v>
       </c>
       <c r="R9" t="n">
-        <v>6516888</v>
+        <v>6517001</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122477989</v>
+        <v>122478011</v>
       </c>
       <c r="B10" t="n">
-        <v>94996</v>
+        <v>94902</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561816</v>
+        <v>561593</v>
       </c>
       <c r="R10" t="n">
-        <v>6517001</v>
+        <v>6516888</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122427282</v>
+        <v>122426577</v>
       </c>
       <c r="B2" t="n">
-        <v>78301</v>
+        <v>94902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R2" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427347</v>
+        <v>122427386</v>
       </c>
       <c r="B3" t="n">
-        <v>94902</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561686</v>
+        <v>561658</v>
       </c>
       <c r="R3" t="n">
         <v>6516859</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429431</v>
+        <v>122427347</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>94902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561619</v>
+        <v>561686</v>
       </c>
       <c r="R4" t="n">
-        <v>6516592</v>
+        <v>6516859</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427386</v>
+        <v>122429431</v>
       </c>
       <c r="B6" t="n">
-        <v>90859</v>
+        <v>105343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561658</v>
+        <v>561619</v>
       </c>
       <c r="R6" t="n">
-        <v>6516859</v>
+        <v>6516592</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122426577</v>
+        <v>122427988</v>
       </c>
       <c r="B7" t="n">
-        <v>94902</v>
+        <v>78656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561634</v>
+        <v>561776</v>
       </c>
       <c r="R7" t="n">
-        <v>6516928</v>
+        <v>6517066</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427988</v>
+        <v>122427282</v>
       </c>
       <c r="B8" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561776</v>
+        <v>561708</v>
       </c>
       <c r="R8" t="n">
-        <v>6517066</v>
+        <v>6516850</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122426577</v>
       </c>
       <c r="B2" t="n">
-        <v>94902</v>
+        <v>94904</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427386</v>
+        <v>122427988</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561658</v>
+        <v>561776</v>
       </c>
       <c r="R3" t="n">
-        <v>6516859</v>
+        <v>6517066</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -882,7 +882,7 @@
         <v>122427347</v>
       </c>
       <c r="B4" t="n">
-        <v>94902</v>
+        <v>94904</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427208</v>
+        <v>122427386</v>
       </c>
       <c r="B5" t="n">
-        <v>94902</v>
+        <v>90853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561708</v>
+        <v>561658</v>
       </c>
       <c r="R5" t="n">
-        <v>6516850</v>
+        <v>6516859</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122429431</v>
+        <v>122427208</v>
       </c>
       <c r="B6" t="n">
-        <v>105343</v>
+        <v>94904</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561619</v>
+        <v>561708</v>
       </c>
       <c r="R6" t="n">
-        <v>6516592</v>
+        <v>6516850</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427988</v>
+        <v>122427282</v>
       </c>
       <c r="B7" t="n">
-        <v>78656</v>
+        <v>78301</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561776</v>
+        <v>561708</v>
       </c>
       <c r="R7" t="n">
-        <v>6517066</v>
+        <v>6516850</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427282</v>
+        <v>122429431</v>
       </c>
       <c r="B8" t="n">
-        <v>78301</v>
+        <v>105346</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,41 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561708</v>
+        <v>561619</v>
       </c>
       <c r="R8" t="n">
-        <v>6516850</v>
+        <v>6516592</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122477989</v>
+        <v>122478011</v>
       </c>
       <c r="B9" t="n">
-        <v>95009</v>
+        <v>94904</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561816</v>
+        <v>561593</v>
       </c>
       <c r="R9" t="n">
-        <v>6517001</v>
+        <v>6516888</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478011</v>
+        <v>122477989</v>
       </c>
       <c r="B10" t="n">
-        <v>94902</v>
+        <v>95011</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561593</v>
+        <v>561816</v>
       </c>
       <c r="R10" t="n">
-        <v>6516888</v>
+        <v>6517001</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427347</v>
+        <v>122429431</v>
       </c>
       <c r="B4" t="n">
-        <v>94904</v>
+        <v>105346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561686</v>
+        <v>561619</v>
       </c>
       <c r="R4" t="n">
-        <v>6516859</v>
+        <v>6516592</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427208</v>
+        <v>122427347</v>
       </c>
       <c r="B6" t="n">
         <v>94904</v>
@@ -1119,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561708</v>
+        <v>561686</v>
       </c>
       <c r="R6" t="n">
-        <v>6516850</v>
+        <v>6516859</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122429431</v>
+        <v>122427208</v>
       </c>
       <c r="B8" t="n">
-        <v>105346</v>
+        <v>94904</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561619</v>
+        <v>561708</v>
       </c>
       <c r="R8" t="n">
-        <v>6516592</v>
+        <v>6516850</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122426577</v>
+        <v>122427347</v>
       </c>
       <c r="B2" t="n">
-        <v>94904</v>
+        <v>94905</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561634</v>
+        <v>561686</v>
       </c>
       <c r="R2" t="n">
-        <v>6516928</v>
+        <v>6516859</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427988</v>
+        <v>122429431</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>105347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561776</v>
+        <v>561619</v>
       </c>
       <c r="R3" t="n">
-        <v>6517066</v>
+        <v>6516592</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122429431</v>
+        <v>122426577</v>
       </c>
       <c r="B4" t="n">
-        <v>105346</v>
+        <v>94905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561619</v>
+        <v>561634</v>
       </c>
       <c r="R4" t="n">
-        <v>6516592</v>
+        <v>6516928</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -984,7 +984,7 @@
         <v>122427386</v>
       </c>
       <c r="B5" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427347</v>
+        <v>122427988</v>
       </c>
       <c r="B6" t="n">
-        <v>94904</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561686</v>
+        <v>561776</v>
       </c>
       <c r="R6" t="n">
-        <v>6516859</v>
+        <v>6517066</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,12 +1173,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
         <v>122427282</v>
       </c>
       <c r="B7" t="n">
-        <v>78301</v>
+        <v>78302</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>122427208</v>
       </c>
       <c r="B8" t="n">
-        <v>94904</v>
+        <v>94905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478011</v>
+        <v>122477989</v>
       </c>
       <c r="B9" t="n">
-        <v>94904</v>
+        <v>95012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561593</v>
+        <v>561816</v>
       </c>
       <c r="R9" t="n">
-        <v>6516888</v>
+        <v>6517001</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122477989</v>
+        <v>122478011</v>
       </c>
       <c r="B10" t="n">
-        <v>95011</v>
+        <v>94905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561816</v>
+        <v>561593</v>
       </c>
       <c r="R10" t="n">
-        <v>6517001</v>
+        <v>6516888</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122427347</v>
+        <v>122427386</v>
       </c>
       <c r="B2" t="n">
-        <v>94905</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561686</v>
+        <v>561658</v>
       </c>
       <c r="R2" t="n">
         <v>6516859</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122429431</v>
+        <v>122427988</v>
       </c>
       <c r="B3" t="n">
-        <v>105347</v>
+        <v>78660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561619</v>
+        <v>561776</v>
       </c>
       <c r="R3" t="n">
-        <v>6516592</v>
+        <v>6517066</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122426577</v>
+        <v>122427347</v>
       </c>
       <c r="B4" t="n">
-        <v>94905</v>
+        <v>94908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561634</v>
+        <v>561686</v>
       </c>
       <c r="R4" t="n">
-        <v>6516928</v>
+        <v>6516859</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122427386</v>
+        <v>122429431</v>
       </c>
       <c r="B5" t="n">
-        <v>90854</v>
+        <v>105350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561658</v>
+        <v>561619</v>
       </c>
       <c r="R5" t="n">
-        <v>6516859</v>
+        <v>6516592</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427988</v>
+        <v>122427282</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78305</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561776</v>
+        <v>561708</v>
       </c>
       <c r="R6" t="n">
-        <v>6517066</v>
+        <v>6516850</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427282</v>
+        <v>122426577</v>
       </c>
       <c r="B7" t="n">
-        <v>78302</v>
+        <v>94908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R7" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
         <v>122427208</v>
       </c>
       <c r="B8" t="n">
-        <v>94905</v>
+        <v>94908</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>122477989</v>
       </c>
       <c r="B9" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>122478011</v>
       </c>
       <c r="B10" t="n">
-        <v>94905</v>
+        <v>94908</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122427386</v>
+        <v>122427208</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>94908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561658</v>
+        <v>561708</v>
       </c>
       <c r="R2" t="n">
-        <v>6516859</v>
+        <v>6516850</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427988</v>
+        <v>122427282</v>
       </c>
       <c r="B3" t="n">
-        <v>78660</v>
+        <v>78305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561776</v>
+        <v>561708</v>
       </c>
       <c r="R3" t="n">
-        <v>6517066</v>
+        <v>6516850</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427347</v>
+        <v>122427386</v>
       </c>
       <c r="B4" t="n">
-        <v>94908</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561686</v>
+        <v>561658</v>
       </c>
       <c r="R4" t="n">
         <v>6516859</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122427282</v>
+        <v>122426577</v>
       </c>
       <c r="B6" t="n">
-        <v>78305</v>
+        <v>94908</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,41 +1095,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R6" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122426577</v>
+        <v>122427988</v>
       </c>
       <c r="B7" t="n">
-        <v>94908</v>
+        <v>78660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,41 +1197,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561634</v>
+        <v>561776</v>
       </c>
       <c r="R7" t="n">
-        <v>6516928</v>
+        <v>6517066</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,19 +1275,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122427208</v>
+        <v>122427347</v>
       </c>
       <c r="B8" t="n">
         <v>94908</v>
@@ -1323,17 +1323,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561708</v>
+        <v>561686</v>
       </c>
       <c r="R8" t="n">
-        <v>6516850</v>
+        <v>6516859</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122477989</v>
+        <v>122478011</v>
       </c>
       <c r="B9" t="n">
-        <v>95015</v>
+        <v>94908</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561816</v>
+        <v>561593</v>
       </c>
       <c r="R9" t="n">
-        <v>6517001</v>
+        <v>6516888</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478011</v>
+        <v>122477989</v>
       </c>
       <c r="B10" t="n">
-        <v>94908</v>
+        <v>95015</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561593</v>
+        <v>561816</v>
       </c>
       <c r="R10" t="n">
-        <v>6516888</v>
+        <v>6517001</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122427208</v>
+        <v>122427282</v>
       </c>
       <c r="B2" t="n">
-        <v>94908</v>
+        <v>78407</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122427282</v>
+        <v>122426577</v>
       </c>
       <c r="B3" t="n">
-        <v>78305</v>
+        <v>95011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orrmossen, Orrmossen, Ög</t>
+          <t>Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561708</v>
+        <v>561634</v>
       </c>
       <c r="R3" t="n">
-        <v>6516850</v>
+        <v>6516928</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122427386</v>
+        <v>122427208</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>95011</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561658</v>
+        <v>561708</v>
       </c>
       <c r="R4" t="n">
-        <v>6516859</v>
+        <v>6516850</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122429431</v>
+        <v>122427988</v>
       </c>
       <c r="B5" t="n">
-        <v>105350</v>
+        <v>78762</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +993,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fågeltorp, Fågeltorp, Ög</t>
+          <t>Orrmossen, Orrmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561619</v>
+        <v>561776</v>
       </c>
       <c r="R5" t="n">
-        <v>6516592</v>
+        <v>6517066</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122426577</v>
+        <v>122429431</v>
       </c>
       <c r="B6" t="n">
-        <v>94908</v>
+        <v>105453</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,37 +1099,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Orrmossen, Ög</t>
+          <t>Fågeltorp, Fågeltorp, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561634</v>
+        <v>561619</v>
       </c>
       <c r="R6" t="n">
-        <v>6516928</v>
+        <v>6516592</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122427988</v>
+        <v>122427386</v>
       </c>
       <c r="B7" t="n">
-        <v>78660</v>
+        <v>90960</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561776</v>
+        <v>561658</v>
       </c>
       <c r="R7" t="n">
-        <v>6517066</v>
+        <v>6516859</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1290,7 +1290,7 @@
         <v>122427347</v>
       </c>
       <c r="B8" t="n">
-        <v>94908</v>
+        <v>95011</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>122478011</v>
       </c>
       <c r="B9" t="n">
-        <v>94908</v>
+        <v>95011</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>122477989</v>
       </c>
       <c r="B10" t="n">
-        <v>95015</v>
+        <v>95118</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>122478011</v>
       </c>
       <c r="B9" t="n">
-        <v>95011</v>
+        <v>95019</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>122477989</v>
       </c>
       <c r="B10" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 3635-2025 artfynd.xlsx
+++ b/artfynd/A 3635-2025 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478011</v>
+        <v>122477989</v>
       </c>
       <c r="B9" t="n">
-        <v>95019</v>
+        <v>95128</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561593</v>
+        <v>561816</v>
       </c>
       <c r="R9" t="n">
-        <v>6516888</v>
+        <v>6517001</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122477989</v>
+        <v>122478011</v>
       </c>
       <c r="B10" t="n">
-        <v>95126</v>
+        <v>95021</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561816</v>
+        <v>561593</v>
       </c>
       <c r="R10" t="n">
-        <v>6517001</v>
+        <v>6516888</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
